--- a/5/search/FY2_Missile1_results/top10_solutions.xlsx
+++ b/5/search/FY2_Missile1_results/top10_solutions.xlsx
@@ -487,247 +487,247 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>297</v>
+        <v>274.5</v>
       </c>
       <c r="B2" t="n">
-        <v>117.6</v>
+        <v>136</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>12427.11426215497</v>
+        <v>12042.68174807595</v>
       </c>
       <c r="F2" t="n">
-        <v>561.7410620435834</v>
+        <v>857.6769704491784</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>12694.06067600182</v>
+        <v>12106.70437018987</v>
       </c>
       <c r="I2" t="n">
-        <v>37.82922582082301</v>
+        <v>44.1924261229459</v>
       </c>
       <c r="J2" t="n">
-        <v>1277.5</v>
+        <v>1223.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.800000000000001</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>225</v>
+        <v>265.5</v>
       </c>
       <c r="B3" t="n">
-        <v>120.4</v>
+        <v>138</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>11318.91474836112</v>
+        <v>11956.69057915823</v>
       </c>
       <c r="F3" t="n">
-        <v>718.9147483611174</v>
+        <v>849.7016317793134</v>
       </c>
       <c r="G3" t="n">
         <v>1400</v>
       </c>
       <c r="H3" t="n">
-        <v>10637.82949672224</v>
+        <v>11891.72644789557</v>
       </c>
       <c r="I3" t="n">
-        <v>37.82949672223481</v>
+        <v>24.25407944828351</v>
       </c>
       <c r="J3" t="n">
-        <v>1086.4</v>
+        <v>1223.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.600000000000001</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="B4" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>12000</v>
+        <v>12276.87922695995</v>
       </c>
       <c r="F4" t="n">
-        <v>616</v>
+        <v>547.8533613995423</v>
       </c>
       <c r="G4" t="n">
         <v>1400</v>
       </c>
       <c r="H4" t="n">
-        <v>12000</v>
+        <v>12449.92874380992</v>
       </c>
       <c r="I4" t="n">
-        <v>28</v>
+        <v>15.2617122742563</v>
       </c>
       <c r="J4" t="n">
-        <v>1223.6</v>
+        <v>1277.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.600000000000001</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="B5" t="n">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>11912.39669957747</v>
+        <v>12428.56703175413</v>
       </c>
       <c r="F5" t="n">
-        <v>846.8945292667229</v>
+        <v>558.8898411661806</v>
       </c>
       <c r="G5" t="n">
         <v>1400</v>
       </c>
       <c r="H5" t="n">
-        <v>11780.99174894368</v>
+        <v>12696.42142660046</v>
       </c>
       <c r="I5" t="n">
-        <v>17.23632316680721</v>
+        <v>33.19599189504356</v>
       </c>
       <c r="J5" t="n">
-        <v>1223.6</v>
+        <v>1277.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>243</v>
+        <v>211.5</v>
       </c>
       <c r="B6" t="n">
-        <v>103.6</v>
+        <v>124</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>11623.73267381586</v>
+        <v>10731.27143544111</v>
       </c>
       <c r="F6" t="n">
-        <v>661.5337927526808</v>
+        <v>622.5221357026684</v>
       </c>
       <c r="G6" t="n">
         <v>1400</v>
       </c>
       <c r="H6" t="n">
-        <v>11294.49876340474</v>
+        <v>9779.725012021943</v>
       </c>
       <c r="I6" t="n">
-        <v>15.37586141127656</v>
+        <v>39.41373747966963</v>
       </c>
       <c r="J6" t="n">
-        <v>1159.9</v>
+        <v>1003.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.400000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>288</v>
+        <v>211.5</v>
       </c>
       <c r="B7" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>12276.87922695995</v>
+        <v>10710.80807149661</v>
       </c>
       <c r="F7" t="n">
-        <v>547.8533613995423</v>
+        <v>609.9821701494855</v>
       </c>
       <c r="G7" t="n">
         <v>1400</v>
       </c>
       <c r="H7" t="n">
-        <v>12449.92874380992</v>
+        <v>9743.914125119072</v>
       </c>
       <c r="I7" t="n">
-        <v>15.2617122742563</v>
+        <v>17.4687977615996</v>
       </c>
       <c r="J7" t="n">
-        <v>1277.5</v>
+        <v>1003.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.400000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>11168.44242532462</v>
+        <v>11912.39669957747</v>
       </c>
       <c r="F8" t="n">
-        <v>568.4424253246202</v>
+        <v>846.8945292667229</v>
       </c>
       <c r="G8" t="n">
         <v>1400</v>
       </c>
       <c r="H8" t="n">
-        <v>10614.07070887437</v>
+        <v>11780.99174894368</v>
       </c>
       <c r="I8" t="n">
-        <v>14.07070887436703</v>
+        <v>17.23632316680721</v>
       </c>
       <c r="J8" t="n">
-        <v>1086.4</v>
+        <v>1223.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.300000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -735,104 +735,104 @@
         <v>252</v>
       </c>
       <c r="B9" t="n">
-        <v>95.2</v>
+        <v>128</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>11764.65265708404</v>
+        <v>11841.78329888003</v>
       </c>
       <c r="F9" t="n">
-        <v>675.6753571896111</v>
+        <v>913.0590636568813</v>
       </c>
       <c r="G9" t="n">
         <v>1400</v>
       </c>
       <c r="H9" t="n">
-        <v>11558.72373203257</v>
+        <v>11564.90407192007</v>
       </c>
       <c r="I9" t="n">
-        <v>41.89129473052071</v>
+        <v>60.91242505642379</v>
       </c>
       <c r="J9" t="n">
         <v>1159.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3.200000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="B10" t="n">
-        <v>75.59999999999999</v>
+        <v>140</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>11719.65978270305</v>
+        <v>11745.76532014585</v>
       </c>
       <c r="F10" t="n">
-        <v>537.2015284170368</v>
+        <v>901.036346454514</v>
       </c>
       <c r="G10" t="n">
         <v>1400</v>
       </c>
       <c r="H10" t="n">
-        <v>11556.12798927982</v>
+        <v>11300.8546304011</v>
       </c>
       <c r="I10" t="n">
-        <v>33.90241999364162</v>
+        <v>27.84995274991365</v>
       </c>
       <c r="J10" t="n">
         <v>1159.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3.100000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>315</v>
+        <v>247.5</v>
       </c>
       <c r="B11" t="n">
-        <v>131.6</v>
+        <v>132</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11797.94314771123</v>
+      </c>
+      <c r="F11" t="n">
+        <v>912.1916068340406</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11444.34365620589</v>
+      </c>
+      <c r="I11" t="n">
+        <v>58.52691879361157</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1159.9</v>
+      </c>
+      <c r="K11" t="n">
         <v>3</v>
-      </c>
-      <c r="E11" t="n">
-        <v>13116.66302884979</v>
-      </c>
-      <c r="F11" t="n">
-        <v>283.3369711502039</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1400</v>
-      </c>
-      <c r="H11" t="n">
-        <v>13395.82878606224</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4.171213937754885</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1355.9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.100000000000001</v>
       </c>
     </row>
   </sheetData>
